--- a/assets/ASSETS LIST.xlsx
+++ b/assets/ASSETS LIST.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VS CODE\AVG_NODE_JS\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15D964E-64D5-4E6F-887C-7C3423056AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90DDD3F-0D56-4E19-B853-ED25970AECD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{594894A2-69C4-4B0F-AAF7-DD797D4CC389}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" activeTab="1" xr2:uid="{594894A2-69C4-4B0F-AAF7-DD797D4CC389}"/>
   </bookViews>
   <sheets>
     <sheet name="Background" sheetId="1" r:id="rId1"/>
     <sheet name="Character" sheetId="2" r:id="rId2"/>
-    <sheet name="Sound" sheetId="3" r:id="rId3"/>
-    <sheet name="BGM" sheetId="4" r:id="rId4"/>
+    <sheet name="Video" sheetId="5" r:id="rId3"/>
+    <sheet name="Sound" sheetId="3" r:id="rId4"/>
+    <sheet name="BGM" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="154">
   <si>
     <t>PATH</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -477,6 +478,166 @@
   </si>
   <si>
     <t>Music</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\music\BGM_01_柔和的農村.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\music\BGM_02_宮廷.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\music\BGM03_神秘神聖的.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\music\BGM04_壓抑不安的.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\music\BGM05_穩定進行的.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\music\BGM06_緊張不安的.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\music\BGM07_威嚴壯麗的.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄉下農莊的風景 漫步在農田與村落之間</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢弘的氣勢 王座前面的富麗堂皇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘又神聖的風格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>壓抑不安的  令人緊張的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穩定進行的 適合各種場合的音樂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不協調的感覺 令人感到害怕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>威嚴壯麗的 不管用在景色還是敘事上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Video</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\mov\Main.mp4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女王揮舞著魔法仗，適合用在封面頁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\mov\001.mp4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊莉莎白在寢室床上害羞的翻滾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊莉莎白在寢室床上邀請你來</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\mov\002.mp4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\mov\003.mp5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\mov\004.mp5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊莉莎白被哥布林綁住掙扎中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊莉莎白被哥布林羞辱後掙扎著</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\VS CODE\AVG_NODE_JS\assets\char\elizabeth_angry_R.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elizabeth with angry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\VS CODE\AVG_NODE_JS\assets\char\elizabeth_angry_L.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\VS CODE\AVG_NODE_JS\assets\char\elizabeth_hurt_L.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elizabeth with hurt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\VS CODE\AVG_NODE_JS\assets\char\elizabeth_hurt_R.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\VS CODE\AVG_NODE_JS\assets\char\elizabeth_hurtAndTired_L.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elizabeth hurt And Tired_L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\VS CODE\AVG_NODE_JS\assets\char\elizabeth_hurtAndTired_R.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\VS CODE\AVG_NODE_JS\assets\char\elizabeth_hurtNeutral_L.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elizabeth hurt but neutral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\VS CODE\AVG_NODE_JS\assets\char\elizabeth_hurtNeutral_R.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>venox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\VS CODE\AVG_NODE_JS\assets\char\venox.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>venox with neutral</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -872,6 +1033,7 @@
   <cols>
     <col min="1" max="1" width="41.77734375" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1124,10 +1286,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C356FA73-3189-4858-BB46-13131BCF5E55}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="2" max="2" width="38.21875" customWidth="1"/>
     <col min="3" max="3" width="64" customWidth="1"/>
     <col min="4" max="4" width="20.5546875" customWidth="1"/>
     <col min="5" max="5" width="27" customWidth="1"/>
@@ -1288,103 +1451,256 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
         <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
         <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
         <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
         <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" t="s">
+        <v>150</v>
+      </c>
+      <c r="D17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>108</v>
       </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" t="s">
         <v>110</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D24" t="s">
         <v>106</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E24" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1395,6 +1711,105 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{138603C5-E7A0-4A79-AEC8-806847BF80BF}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="1">
+        <v>5.5555555555555558E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="1">
+        <v>4.1666666666666666E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="1">
+        <v>4.1666666666666666E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4.1666666666666666E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" s="1">
+        <v>4.1666666666666666E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C300BE-BB8E-42D9-81C7-BCEF5A4F5F69}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -1619,13 +2034,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2694E2-8434-46CF-9FBB-E6B459A0CDB4}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="2" max="2" width="52.77734375" customWidth="1"/>
     <col min="3" max="3" width="20.88671875" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
@@ -1658,6 +2073,104 @@
         <v>2.2083333333333335</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2.1527777777777778E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2.1527777777777778E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2.1527777777777778E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2.1527777777777778E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2.1527777777777778E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2.1527777777777778E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2.1527777777777778E-2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
